--- a/job-search/Job_Application_Tracker.xlsx
+++ b/job-search/Job_Application_Tracker.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +171,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -814,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -828,6 +831,8 @@
     <col width="46" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -886,6 +891,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Resume Variant</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>Tailored Materials</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="n">
@@ -929,6 +944,16 @@
       </c>
       <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M2" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -972,6 +997,16 @@
       </c>
       <c r="J3" s="10" t="inlineStr"/>
       <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -1019,6 +1054,16 @@
       </c>
       <c r="J4" s="10" t="inlineStr"/>
       <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -1066,6 +1111,16 @@
       </c>
       <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1109,6 +1164,16 @@
       </c>
       <c r="J6" s="10" t="inlineStr"/>
       <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1152,6 +1217,16 @@
       </c>
       <c r="J7" s="10" t="inlineStr"/>
       <c r="K7" s="10" t="inlineStr"/>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -1199,6 +1274,8 @@
       </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="26" t="inlineStr"/>
+      <c r="M8" s="26" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -1246,6 +1323,8 @@
       </c>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="26" t="inlineStr"/>
+      <c r="M9" s="26" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -1293,6 +1372,16 @@
       </c>
       <c r="J10" s="10" t="inlineStr"/>
       <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #7</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1340,6 +1429,16 @@
       </c>
       <c r="J11" s="10" t="inlineStr"/>
       <c r="K11" s="10" t="inlineStr"/>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -1383,6 +1482,16 @@
       </c>
       <c r="J12" s="10" t="inlineStr"/>
       <c r="K12" s="10" t="inlineStr"/>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M12" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #9</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1426,6 +1535,16 @@
       </c>
       <c r="J13" s="10" t="inlineStr"/>
       <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #10</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1473,6 +1592,16 @@
       </c>
       <c r="J14" s="10" t="inlineStr"/>
       <c r="K14" s="10" t="inlineStr"/>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
@@ -1520,6 +1649,8 @@
       </c>
       <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr"/>
+      <c r="L15" s="26" t="inlineStr"/>
+      <c r="M15" s="26" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -1567,6 +1698,16 @@
       </c>
       <c r="J16" s="10" t="inlineStr"/>
       <c r="K16" s="10" t="inlineStr"/>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M16" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #12</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1614,6 +1755,16 @@
       </c>
       <c r="J17" s="10" t="inlineStr"/>
       <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #13</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -1657,6 +1808,16 @@
       </c>
       <c r="J18" s="10" t="inlineStr"/>
       <c r="K18" s="10" t="inlineStr"/>
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M18" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #14</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -1704,6 +1865,16 @@
       </c>
       <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #15</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1751,6 +1922,16 @@
       </c>
       <c r="J20" s="10" t="inlineStr"/>
       <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M20" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #16</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
@@ -1794,6 +1975,8 @@
       </c>
       <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="26" t="inlineStr"/>
+      <c r="M21" s="26" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
@@ -1837,6 +2020,8 @@
       </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="26" t="inlineStr"/>
+      <c r="M22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
@@ -1884,6 +2069,8 @@
       </c>
       <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="26" t="inlineStr"/>
+      <c r="M23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -1931,6 +2118,16 @@
       </c>
       <c r="J24" s="10" t="inlineStr"/>
       <c r="K24" s="10" t="inlineStr"/>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M24" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #17</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -1978,6 +2175,16 @@
       </c>
       <c r="J25" s="10" t="inlineStr"/>
       <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M25" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #18</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -2025,6 +2232,16 @@
       </c>
       <c r="J26" s="10" t="inlineStr"/>
       <c r="K26" s="10" t="inlineStr"/>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #19</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
@@ -2072,6 +2289,8 @@
       </c>
       <c r="J27" s="16" t="inlineStr"/>
       <c r="K27" s="16" t="inlineStr"/>
+      <c r="L27" s="26" t="inlineStr"/>
+      <c r="M27" s="26" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
@@ -2119,6 +2338,8 @@
       </c>
       <c r="J28" s="13" t="inlineStr"/>
       <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="26" t="inlineStr"/>
+      <c r="M28" s="26" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -2166,6 +2387,16 @@
       </c>
       <c r="J29" s="10" t="inlineStr"/>
       <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #20</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
@@ -2213,6 +2444,8 @@
       </c>
       <c r="J30" s="13" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr"/>
+      <c r="L30" s="26" t="inlineStr"/>
+      <c r="M30" s="26" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
@@ -2260,6 +2493,8 @@
       </c>
       <c r="J31" s="13" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr"/>
+      <c r="L31" s="26" t="inlineStr"/>
+      <c r="M31" s="26" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
@@ -2303,6 +2538,8 @@
       </c>
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="26" t="inlineStr"/>
+      <c r="M32" s="26" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
@@ -2350,6 +2587,8 @@
       </c>
       <c r="J33" s="16" t="inlineStr"/>
       <c r="K33" s="16" t="inlineStr"/>
+      <c r="L33" s="26" t="inlineStr"/>
+      <c r="M33" s="26" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -2397,6 +2636,16 @@
       </c>
       <c r="J34" s="10" t="inlineStr"/>
       <c r="K34" s="10" t="inlineStr"/>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #21</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -2444,6 +2693,16 @@
       </c>
       <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #22</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -2491,6 +2750,16 @@
       </c>
       <c r="J36" s="10" t="inlineStr"/>
       <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #23</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
@@ -2538,6 +2807,8 @@
       </c>
       <c r="J37" s="13" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr"/>
+      <c r="L37" s="26" t="inlineStr"/>
+      <c r="M37" s="26" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
@@ -2585,6 +2856,8 @@
       </c>
       <c r="J38" s="16" t="inlineStr"/>
       <c r="K38" s="16" t="inlineStr"/>
+      <c r="L38" s="26" t="inlineStr"/>
+      <c r="M38" s="26" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
@@ -2632,6 +2905,8 @@
       </c>
       <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="13" t="inlineStr"/>
+      <c r="L39" s="26" t="inlineStr"/>
+      <c r="M39" s="26" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -2679,6 +2954,16 @@
       </c>
       <c r="J40" s="10" t="inlineStr"/>
       <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M40" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #24</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
@@ -2726,6 +3011,8 @@
       </c>
       <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr"/>
+      <c r="L41" s="26" t="inlineStr"/>
+      <c r="M41" s="26" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
@@ -2773,6 +3060,8 @@
       </c>
       <c r="J42" s="16" t="inlineStr"/>
       <c r="K42" s="16" t="inlineStr"/>
+      <c r="L42" s="26" t="inlineStr"/>
+      <c r="M42" s="26" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -2820,6 +3109,16 @@
       </c>
       <c r="J43" s="10" t="inlineStr"/>
       <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M43" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #25</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
@@ -2867,6 +3166,16 @@
       </c>
       <c r="J44" s="10" t="inlineStr"/>
       <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M44" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #26</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
@@ -2914,6 +3223,8 @@
       </c>
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr"/>
+      <c r="L45" s="26" t="inlineStr"/>
+      <c r="M45" s="26" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
@@ -2961,6 +3272,16 @@
       </c>
       <c r="J46" s="10" t="inlineStr"/>
       <c r="K46" s="10" t="inlineStr"/>
+      <c r="L46" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M46" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #27</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
@@ -3008,6 +3329,16 @@
       </c>
       <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #28</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
@@ -3055,6 +3386,8 @@
       </c>
       <c r="J48" s="16" t="inlineStr"/>
       <c r="K48" s="16" t="inlineStr"/>
+      <c r="L48" s="26" t="inlineStr"/>
+      <c r="M48" s="26" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
@@ -3102,6 +3435,8 @@
       </c>
       <c r="J49" s="16" t="inlineStr"/>
       <c r="K49" s="16" t="inlineStr"/>
+      <c r="L49" s="26" t="inlineStr"/>
+      <c r="M49" s="26" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
@@ -3149,6 +3484,8 @@
       </c>
       <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="13" t="inlineStr"/>
+      <c r="L50" s="26" t="inlineStr"/>
+      <c r="M50" s="26" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
@@ -3196,6 +3533,8 @@
       </c>
       <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr"/>
+      <c r="L51" s="26" t="inlineStr"/>
+      <c r="M51" s="26" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n">
@@ -3243,6 +3582,8 @@
       </c>
       <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="13" t="inlineStr"/>
+      <c r="L52" s="26" t="inlineStr"/>
+      <c r="M52" s="26" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
@@ -3290,6 +3631,8 @@
       </c>
       <c r="J53" s="16" t="inlineStr"/>
       <c r="K53" s="16" t="inlineStr"/>
+      <c r="L53" s="26" t="inlineStr"/>
+      <c r="M53" s="26" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -3337,6 +3680,16 @@
       </c>
       <c r="J54" s="10" t="inlineStr"/>
       <c r="K54" s="10" t="inlineStr"/>
+      <c r="L54" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M54" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #29</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -3384,6 +3737,16 @@
       </c>
       <c r="J55" s="10" t="inlineStr"/>
       <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M55" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n">
@@ -3431,6 +3794,8 @@
       </c>
       <c r="J56" s="13" t="inlineStr"/>
       <c r="K56" s="13" t="inlineStr"/>
+      <c r="L56" s="26" t="inlineStr"/>
+      <c r="M56" s="26" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -3478,6 +3843,16 @@
       </c>
       <c r="J57" s="10" t="inlineStr"/>
       <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M57" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #31</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -3525,6 +3900,16 @@
       </c>
       <c r="J58" s="10" t="inlineStr"/>
       <c r="K58" s="10" t="inlineStr"/>
+      <c r="L58" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M58" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #32</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n">
@@ -3572,6 +3957,8 @@
       </c>
       <c r="J59" s="13" t="inlineStr"/>
       <c r="K59" s="13" t="inlineStr"/>
+      <c r="L59" s="26" t="inlineStr"/>
+      <c r="M59" s="26" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="18" t="n">
@@ -3619,6 +4006,8 @@
       </c>
       <c r="J60" s="19" t="inlineStr"/>
       <c r="K60" s="19" t="inlineStr"/>
+      <c r="L60" s="26" t="inlineStr"/>
+      <c r="M60" s="26" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -3666,6 +4055,16 @@
       </c>
       <c r="J61" s="10" t="inlineStr"/>
       <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M61" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #33</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -3713,6 +4112,16 @@
       </c>
       <c r="J62" s="10" t="inlineStr"/>
       <c r="K62" s="10" t="inlineStr"/>
+      <c r="L62" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M62" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #34</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -3760,6 +4169,16 @@
       </c>
       <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M63" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #35</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n">
@@ -3807,6 +4226,8 @@
       </c>
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="13" t="inlineStr"/>
+      <c r="L64" s="26" t="inlineStr"/>
+      <c r="M64" s="26" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -3854,6 +4275,16 @@
       </c>
       <c r="J65" s="10" t="inlineStr"/>
       <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M65" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #36</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -3901,6 +4332,16 @@
       </c>
       <c r="J66" s="10" t="inlineStr"/>
       <c r="K66" s="10" t="inlineStr"/>
+      <c r="L66" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M66" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #37</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -3948,6 +4389,16 @@
       </c>
       <c r="J67" s="10" t="inlineStr"/>
       <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M67" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #38</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n">
@@ -3995,6 +4446,8 @@
       </c>
       <c r="J68" s="13" t="inlineStr"/>
       <c r="K68" s="13" t="inlineStr"/>
+      <c r="L68" s="26" t="inlineStr"/>
+      <c r="M68" s="26" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
@@ -4042,6 +4495,8 @@
       </c>
       <c r="J69" s="16" t="inlineStr"/>
       <c r="K69" s="16" t="inlineStr"/>
+      <c r="L69" s="26" t="inlineStr"/>
+      <c r="M69" s="26" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n">
@@ -4089,6 +4544,8 @@
       </c>
       <c r="J70" s="13" t="inlineStr"/>
       <c r="K70" s="13" t="inlineStr"/>
+      <c r="L70" s="26" t="inlineStr"/>
+      <c r="M70" s="26" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
@@ -4136,6 +4593,16 @@
       </c>
       <c r="J71" s="10" t="inlineStr"/>
       <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M71" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #39</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -4183,6 +4650,16 @@
       </c>
       <c r="J72" s="10" t="inlineStr"/>
       <c r="K72" s="10" t="inlineStr"/>
+      <c r="L72" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M72" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #40</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n">
@@ -4230,6 +4707,8 @@
       </c>
       <c r="J73" s="13" t="inlineStr"/>
       <c r="K73" s="13" t="inlineStr"/>
+      <c r="L73" s="26" t="inlineStr"/>
+      <c r="M73" s="26" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n">
@@ -4277,6 +4756,16 @@
       </c>
       <c r="J74" s="10" t="inlineStr"/>
       <c r="K74" s="10" t="inlineStr"/>
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M74" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #41</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
@@ -4324,6 +4813,8 @@
       </c>
       <c r="J75" s="13" t="inlineStr"/>
       <c r="K75" s="13" t="inlineStr"/>
+      <c r="L75" s="26" t="inlineStr"/>
+      <c r="M75" s="26" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
@@ -4371,6 +4862,8 @@
       </c>
       <c r="J76" s="13" t="inlineStr"/>
       <c r="K76" s="13" t="inlineStr"/>
+      <c r="L76" s="26" t="inlineStr"/>
+      <c r="M76" s="26" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -4418,6 +4911,16 @@
       </c>
       <c r="J77" s="10" t="inlineStr"/>
       <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="26" t="inlineStr">
+        <is>
+          <t>AM — Mohamed_Amer_CV_ATS_AM.pdf</t>
+        </is>
+      </c>
+      <c r="M77" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #42</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
@@ -4465,6 +4968,8 @@
       </c>
       <c r="J78" s="16" t="inlineStr"/>
       <c r="K78" s="16" t="inlineStr"/>
+      <c r="L78" s="26" t="inlineStr"/>
+      <c r="M78" s="26" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n">
@@ -4512,6 +5017,8 @@
       </c>
       <c r="J79" s="13" t="inlineStr"/>
       <c r="K79" s="13" t="inlineStr"/>
+      <c r="L79" s="26" t="inlineStr"/>
+      <c r="M79" s="26" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
@@ -4559,6 +5066,8 @@
       </c>
       <c r="J80" s="13" t="inlineStr"/>
       <c r="K80" s="13" t="inlineStr"/>
+      <c r="L80" s="26" t="inlineStr"/>
+      <c r="M80" s="26" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
@@ -4606,6 +5115,8 @@
       </c>
       <c r="J81" s="13" t="inlineStr"/>
       <c r="K81" s="13" t="inlineStr"/>
+      <c r="L81" s="26" t="inlineStr"/>
+      <c r="M81" s="26" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
@@ -4653,6 +5164,8 @@
       </c>
       <c r="J82" s="13" t="inlineStr"/>
       <c r="K82" s="13" t="inlineStr"/>
+      <c r="L82" s="26" t="inlineStr"/>
+      <c r="M82" s="26" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
@@ -4700,6 +5213,8 @@
       </c>
       <c r="J83" s="16" t="inlineStr"/>
       <c r="K83" s="16" t="inlineStr"/>
+      <c r="L83" s="26" t="inlineStr"/>
+      <c r="M83" s="26" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n">
@@ -4747,6 +5262,8 @@
       </c>
       <c r="J84" s="13" t="inlineStr"/>
       <c r="K84" s="13" t="inlineStr"/>
+      <c r="L84" s="26" t="inlineStr"/>
+      <c r="M84" s="26" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
@@ -4794,6 +5311,8 @@
       </c>
       <c r="J85" s="16" t="inlineStr"/>
       <c r="K85" s="16" t="inlineStr"/>
+      <c r="L85" s="26" t="inlineStr"/>
+      <c r="M85" s="26" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n">
@@ -4841,6 +5360,8 @@
       </c>
       <c r="J86" s="13" t="inlineStr"/>
       <c r="K86" s="13" t="inlineStr"/>
+      <c r="L86" s="26" t="inlineStr"/>
+      <c r="M86" s="26" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
@@ -4888,6 +5409,8 @@
       </c>
       <c r="J87" s="16" t="inlineStr"/>
       <c r="K87" s="16" t="inlineStr"/>
+      <c r="L87" s="26" t="inlineStr"/>
+      <c r="M87" s="26" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n">
@@ -4935,6 +5458,8 @@
       </c>
       <c r="J88" s="13" t="inlineStr"/>
       <c r="K88" s="13" t="inlineStr"/>
+      <c r="L88" s="26" t="inlineStr"/>
+      <c r="M88" s="26" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
@@ -4982,7 +5507,18 @@
       </c>
       <c r="J89" s="10" t="inlineStr"/>
       <c r="K89" s="10" t="inlineStr"/>
-    </row>
+      <c r="L89" s="26" t="inlineStr">
+        <is>
+          <t>CSM — Mohamed_Amer_CV_ATS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="M89" s="26" t="inlineStr">
+        <is>
+          <t>Ready — job-search/Tailored_Applications_Tier1.md #43</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
